--- a/excel/Afranga.xlsx
+++ b/excel/Afranga.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Afranga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-v2\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CB66F3-030C-406A-B6C0-AAA73EAB2672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD71F8C-0C73-4DB7-8184-D9BDDC488DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="K3" s="17">
         <f ca="1">'10000159'!B12</f>
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L3" s="17" t="str">
         <f ca="1">'10000159'!P3</f>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="T3" s="32">
         <f>W3-R3</f>
-        <v>0.92000000000001592</v>
+        <v>1.5300000000000296</v>
       </c>
       <c r="U3" s="32">
         <f>SUM(M3:M100)</f>
@@ -1990,27 +1990,27 @@
       </c>
       <c r="V3" s="32">
         <f>SUM(N3:N100)-AA3</f>
-        <v>12.519999999999998</v>
+        <v>13.130000000000003</v>
       </c>
       <c r="W3" s="32">
         <f>Q3+V3+S3</f>
-        <v>304.39</v>
+        <v>305</v>
       </c>
       <c r="X3" s="32">
         <f>W3-Q3</f>
-        <v>14.389999999999986</v>
+        <v>15</v>
       </c>
       <c r="Y3" s="35">
         <f>(W3-Q3)/Q3</f>
-        <v>4.9620689655172363E-2</v>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="Z3" s="35">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>9.4052109122276323E-2</v>
+        <v>9.5573046803474435E-2</v>
       </c>
       <c r="AA3" s="32">
         <f>SUM(O3:O100)</f>
-        <v>1.4600000000000002</v>
+        <v>1.5300000000000002</v>
       </c>
       <c r="AC3" s="3" t="str">
         <f ca="1">'10000159'!Z3</f>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="K4" s="17">
         <f ca="1">'10000160'!B12</f>
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="L4" s="17" t="str">
         <f ca="1">'10000160'!P3</f>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="K5" s="17">
         <f ca="1">'10000158'!B12</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L5" s="17" t="str">
         <f ca="1">'10000158'!P3</f>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K6" s="17">
         <f ca="1">'10000170'!B12</f>
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L6" s="17" t="str">
         <f ca="1">'10000170'!P3</f>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="K7" s="17">
         <f ca="1">'10000212'!B12</f>
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L7" s="17" t="str">
         <f ca="1">'10000212'!P3</f>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="K8" s="17">
         <f ca="1">'10000263'!B12</f>
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="L8" s="17" t="str">
         <f ca="1">'10000263'!P3</f>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="K9" s="17">
         <f ca="1">'10000288'!B12</f>
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="L9" s="17" t="str">
         <f ca="1">'10000288'!P3</f>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="K10" s="17">
         <f ca="1">'10000437'!B12</f>
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="L10" s="17" t="str">
         <f ca="1">'10000437'!P3</f>
@@ -2478,11 +2478,11 @@
       </c>
       <c r="N10" s="3">
         <f>'10000437'!L3</f>
-        <v>0.94</v>
+        <v>1.23</v>
       </c>
       <c r="O10" s="3">
         <f>'10000437'!M3</f>
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="P10" s="9"/>
       <c r="AC10" s="3" t="str">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="K11" s="17">
         <f ca="1">'10000591'!B12</f>
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="L11" s="17" t="str">
         <f ca="1">'10000591'!P3</f>
@@ -2544,11 +2544,11 @@
       </c>
       <c r="N11" s="3">
         <f>'10000591'!L3</f>
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="O11" s="3">
         <f>'10000591'!M3</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="P11" s="9"/>
       <c r="AC11" s="3" t="str">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="K12" s="17">
         <f ca="1">'10000722'!B12</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L12" s="17" t="str">
         <f ca="1">'10000722'!P3</f>
@@ -2610,11 +2610,11 @@
       </c>
       <c r="N12" s="3">
         <f>'10000722'!L3</f>
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="O12" s="3">
         <f>'10000722'!M3</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="P12" s="9"/>
       <c r="AC12" s="3" t="str">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="K13" s="17">
         <f ca="1">'10001244'!B12</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L13" s="17" t="str">
         <f ca="1">'10001244'!P3</f>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -10013,14 +10013,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="28">
         <f>Overview!W3</f>
-        <v>304.39</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -11438,11 +11438,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -11481,12 +11481,25 @@
       <c r="B4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="D4" s="10">
+        <v>46231</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46231</v>
+      </c>
+      <c r="F4" s="17">
+        <f t="shared" ref="F4:F10" si="0">IF(E4&gt;0,E4-D4,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.02</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -11503,7 +11516,7 @@
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
       <c r="F5" s="17" t="str">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G5" s="3"/>
@@ -11512,11 +11525,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46231</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -11652,7 +11665,7 @@
       <c r="D11" s="10"/>
       <c r="E11" s="6"/>
       <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F11:F52" si="3">IF(E11&gt;0,E11-D11,"")</f>
         <v/>
       </c>
       <c r="G11" s="2"/>
@@ -11674,12 +11687,12 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G12" s="2"/>
@@ -11701,7 +11714,7 @@
       <c r="D13" s="10"/>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G13" s="2"/>
@@ -11724,7 +11737,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G14" s="2"/>
@@ -11750,7 +11763,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="6"/>
       <c r="F15" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G15" s="2"/>
@@ -11783,7 +11796,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="6"/>
       <c r="F16" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G16" s="2"/>
@@ -11810,7 +11823,7 @@
       <c r="D17" s="10"/>
       <c r="E17" s="6"/>
       <c r="F17" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G17" s="2"/>
@@ -11830,7 +11843,7 @@
       <c r="D18" s="10"/>
       <c r="E18" s="6"/>
       <c r="F18" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G18" s="2"/>
@@ -11850,7 +11863,7 @@
       <c r="D19" s="10"/>
       <c r="E19" s="6"/>
       <c r="F19" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G19" s="2"/>
@@ -11870,7 +11883,7 @@
       <c r="D20" s="10"/>
       <c r="E20" s="6"/>
       <c r="F20" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G20" s="2"/>
@@ -11890,7 +11903,7 @@
       <c r="D21" s="10"/>
       <c r="E21" s="6"/>
       <c r="F21" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G21" s="2"/>
@@ -11910,7 +11923,7 @@
       <c r="D22" s="10"/>
       <c r="E22" s="6"/>
       <c r="F22" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G22" s="2"/>
@@ -11930,7 +11943,7 @@
       <c r="D23" s="10"/>
       <c r="E23" s="6"/>
       <c r="F23" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G23" s="2"/>
@@ -11950,7 +11963,7 @@
       <c r="D24" s="10"/>
       <c r="E24" s="6"/>
       <c r="F24" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G24" s="2"/>
@@ -11970,7 +11983,7 @@
       <c r="D25" s="10"/>
       <c r="E25" s="6"/>
       <c r="F25" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G25" s="2"/>
@@ -11990,7 +12003,7 @@
       <c r="D26" s="10"/>
       <c r="E26" s="6"/>
       <c r="F26" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G26" s="2"/>
@@ -12010,7 +12023,7 @@
       <c r="D27" s="10"/>
       <c r="E27" s="6"/>
       <c r="F27" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G27" s="2"/>
@@ -12030,7 +12043,7 @@
       <c r="D28" s="10"/>
       <c r="E28" s="6"/>
       <c r="F28" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G28" s="2"/>
@@ -12050,7 +12063,7 @@
       <c r="D29" s="10"/>
       <c r="E29" s="6"/>
       <c r="F29" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G29" s="2"/>
@@ -12070,7 +12083,7 @@
       <c r="D30" s="10"/>
       <c r="E30" s="6"/>
       <c r="F30" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G30" s="2"/>
@@ -12090,7 +12103,7 @@
       <c r="D31" s="10"/>
       <c r="E31" s="6"/>
       <c r="F31" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G31" s="2"/>
@@ -12110,7 +12123,7 @@
       <c r="D32" s="10"/>
       <c r="E32" s="6"/>
       <c r="F32" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G32" s="2"/>
@@ -12130,7 +12143,7 @@
       <c r="D33" s="10"/>
       <c r="E33" s="6"/>
       <c r="F33" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G33" s="2"/>
@@ -12150,7 +12163,7 @@
       <c r="D34" s="10"/>
       <c r="E34" s="6"/>
       <c r="F34" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G34" s="2"/>
@@ -12170,7 +12183,7 @@
       <c r="D35" s="10"/>
       <c r="E35" s="6"/>
       <c r="F35" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G35" s="2"/>
@@ -12190,7 +12203,7 @@
       <c r="D36" s="10"/>
       <c r="E36" s="6"/>
       <c r="F36" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G36" s="2"/>
@@ -12210,7 +12223,7 @@
       <c r="D37" s="10"/>
       <c r="E37" s="6"/>
       <c r="F37" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G37" s="2"/>
@@ -12230,7 +12243,7 @@
       <c r="D38" s="10"/>
       <c r="E38" s="6"/>
       <c r="F38" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G38" s="2"/>
@@ -12250,7 +12263,7 @@
       <c r="D39" s="10"/>
       <c r="E39" s="6"/>
       <c r="F39" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G39" s="2"/>
@@ -12270,7 +12283,7 @@
       <c r="D40" s="10"/>
       <c r="E40" s="6"/>
       <c r="F40" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G40" s="2"/>
@@ -12290,7 +12303,7 @@
       <c r="D41" s="10"/>
       <c r="E41" s="6"/>
       <c r="F41" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G41" s="2"/>
@@ -12310,7 +12323,7 @@
       <c r="D42" s="10"/>
       <c r="E42" s="6"/>
       <c r="F42" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G42" s="2"/>
@@ -12330,7 +12343,7 @@
       <c r="D43" s="10"/>
       <c r="E43" s="6"/>
       <c r="F43" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G43" s="2"/>
@@ -12350,7 +12363,7 @@
       <c r="D44" s="10"/>
       <c r="E44" s="6"/>
       <c r="F44" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G44" s="2"/>
@@ -12370,7 +12383,7 @@
       <c r="D45" s="10"/>
       <c r="E45" s="6"/>
       <c r="F45" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G45" s="2"/>
@@ -12390,7 +12403,7 @@
       <c r="D46" s="10"/>
       <c r="E46" s="6"/>
       <c r="F46" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G46" s="2"/>
@@ -12410,7 +12423,7 @@
       <c r="D47" s="10"/>
       <c r="E47" s="6"/>
       <c r="F47" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G47" s="2"/>
@@ -12430,7 +12443,7 @@
       <c r="D48" s="10"/>
       <c r="E48" s="6"/>
       <c r="F48" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G48" s="2"/>
@@ -12450,7 +12463,7 @@
       <c r="D49" s="10"/>
       <c r="E49" s="6"/>
       <c r="F49" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G49" s="2"/>
@@ -12470,7 +12483,7 @@
       <c r="D50" s="10"/>
       <c r="E50" s="6"/>
       <c r="F50" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G50" s="2"/>
@@ -12490,7 +12503,7 @@
       <c r="D51" s="10"/>
       <c r="E51" s="6"/>
       <c r="F51" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G51" s="2"/>
@@ -12510,7 +12523,7 @@
       <c r="D52" s="10"/>
       <c r="E52" s="6"/>
       <c r="F52" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="G52" s="2"/>
@@ -12537,12 +12550,12 @@
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.2</v>
+        <f t="shared" ref="H53:I53" si="4">SUM(H3:H52)</f>
+        <v>0.38</v>
       </c>
       <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0.02</v>
+        <f t="shared" si="4"/>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -12717,11 +12730,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -12792,15 +12805,25 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="str">
+      <c r="D5" s="10">
+        <v>46231</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46231</v>
+      </c>
+      <c r="F5" s="17">
         <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.02</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -12826,11 +12849,11 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46231</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -12966,7 +12989,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -13830,11 +13853,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -14009,11 +14032,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.94</v>
+        <v>1.23</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -14115,15 +14138,25 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
+      <c r="D6" s="10">
+        <v>46211</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46211</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.03</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -14149,11 +14182,11 @@
       <c r="J7" s="14"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46211</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -14267,7 +14300,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -15131,11 +15164,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.94</v>
+        <v>1.23</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -15589,7 +15622,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -16911,7 +16944,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -18253,7 +18286,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>

--- a/excel/Afranga.xlsx
+++ b/excel/Afranga.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-v2\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Afranga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD71F8C-0C73-4DB7-8184-D9BDDC488DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918EEC03-F886-49BC-9D7C-E0B9967570FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="10001244" sheetId="35" r:id="rId3"/>
-    <sheet name="10000722" sheetId="34" r:id="rId4"/>
-    <sheet name="10000591" sheetId="33" r:id="rId5"/>
-    <sheet name="10000437" sheetId="32" r:id="rId6"/>
-    <sheet name="10000288" sheetId="31" r:id="rId7"/>
-    <sheet name="10000263" sheetId="30" r:id="rId8"/>
-    <sheet name="10000212" sheetId="29" r:id="rId9"/>
-    <sheet name="10000170" sheetId="28" r:id="rId10"/>
-    <sheet name="10000158" sheetId="27" r:id="rId11"/>
-    <sheet name="10000160" sheetId="26" r:id="rId12"/>
-    <sheet name="10000159" sheetId="24" r:id="rId13"/>
+    <sheet name="10001352" sheetId="36" r:id="rId3"/>
+    <sheet name="10001244" sheetId="35" r:id="rId4"/>
+    <sheet name="10000722" sheetId="34" r:id="rId5"/>
+    <sheet name="10000591" sheetId="33" r:id="rId6"/>
+    <sheet name="10000437" sheetId="32" r:id="rId7"/>
+    <sheet name="10000288" sheetId="31" r:id="rId8"/>
+    <sheet name="10000263" sheetId="30" r:id="rId9"/>
+    <sheet name="10000212" sheetId="29" r:id="rId10"/>
+    <sheet name="10000170" sheetId="28" r:id="rId11"/>
+    <sheet name="10000158" sheetId="27" r:id="rId12"/>
+    <sheet name="10000160" sheetId="26" r:id="rId13"/>
+    <sheet name="10000159" sheetId="24" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="62">
   <si>
     <t>Paskola</t>
   </si>
@@ -228,6 +229,12 @@
   </si>
   <si>
     <t>Viso</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ID 205174291 - 10001352</t>
   </si>
 </sst>
 </file>
@@ -522,7 +529,49 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="56">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -907,7 +956,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E90775C4-BAB6-4D13-B640-C0DF738ECBD6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{275BD4ED-4B57-4162-83D2-854F97D2036F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -963,6 +1012,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED2ECCA0-80A3-426C-A608-F4925BC22406}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F1463A4-8800-48EC-B2CB-1A3F6A0C6A19}"/>
             </a:ext>
           </a:extLst>
@@ -998,7 +1103,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1075,7 +1180,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCBE527D-4A23-4E4A-AC7E-1AFBA1CAB55A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E90775C4-BAB6-4D13-B640-C0DF738ECBD6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1131,7 +1236,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EE4D48B-03EB-4D83-A46B-315D6745E732}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCBE527D-4A23-4E4A-AC7E-1AFBA1CAB55A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1187,7 +1292,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47FF4319-555E-4F69-8EBB-76B3297F2074}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EE4D48B-03EB-4D83-A46B-315D6745E732}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1243,7 +1348,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A793C6-D2B0-460B-B330-1B6E7FE7CDFC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47FF4319-555E-4F69-8EBB-76B3297F2074}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1299,7 +1404,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D16E9C-0AB8-45AB-928F-FA2477F6577D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A793C6-D2B0-460B-B330-1B6E7FE7CDFC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1355,7 +1460,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E47B75D7-93D2-48E8-AD9A-78030D97E09E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D16E9C-0AB8-45AB-928F-FA2477F6577D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1411,7 +1516,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7DEFBA9-93E5-4EF0-9E7B-D6DF25DCCADD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E47B75D7-93D2-48E8-AD9A-78030D97E09E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1467,7 +1572,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED2ECCA0-80A3-426C-A608-F4925BC22406}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7DEFBA9-93E5-4EF0-9E7B-D6DF25DCCADD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1949,7 +2054,7 @@
       </c>
       <c r="K3" s="17">
         <f ca="1">'10000159'!B12</f>
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="L3" s="17" t="str">
         <f ca="1">'10000159'!P3</f>
@@ -1961,20 +2066,20 @@
       </c>
       <c r="N3" s="3">
         <f>'10000159'!L3</f>
-        <v>4.24</v>
+        <v>4.78</v>
       </c>
       <c r="O3" s="3">
         <f>'10000159'!M3</f>
-        <v>0.39999999999999997</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="32">
         <f>Pinigai!I2</f>
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="R3" s="32">
         <f>SUM(H3:H100)-U3</f>
-        <v>303.46999999999997</v>
+        <v>315.59999999999997</v>
       </c>
       <c r="S3" s="33">
         <f>Pinigai!H2</f>
@@ -1982,35 +2087,35 @@
       </c>
       <c r="T3" s="32">
         <f>W3-R3</f>
-        <v>1.5300000000000296</v>
+        <v>0</v>
       </c>
       <c r="U3" s="32">
         <f>SUM(M3:M100)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V3" s="32">
         <f>SUM(N3:N100)-AA3</f>
-        <v>13.130000000000003</v>
+        <v>13.73</v>
       </c>
       <c r="W3" s="32">
         <f>Q3+V3+S3</f>
-        <v>305</v>
+        <v>315.60000000000002</v>
       </c>
       <c r="X3" s="32">
         <f>W3-Q3</f>
-        <v>15</v>
+        <v>15.600000000000023</v>
       </c>
       <c r="Y3" s="35">
         <f>(W3-Q3)/Q3</f>
-        <v>5.1724137931034482E-2</v>
+        <v>5.2000000000000074E-2</v>
       </c>
       <c r="Z3" s="35">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>9.5573046803474435E-2</v>
+        <v>9.646490216255188E-2</v>
       </c>
       <c r="AA3" s="32">
         <f>SUM(O3:O100)</f>
-        <v>1.5300000000000002</v>
+        <v>1.6000000000000005</v>
       </c>
       <c r="AC3" s="3" t="str">
         <f ca="1">'10000159'!Z3</f>
@@ -2059,7 +2164,7 @@
       </c>
       <c r="K4" s="17">
         <f ca="1">'10000160'!B12</f>
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="L4" s="17" t="str">
         <f ca="1">'10000160'!P3</f>
@@ -2071,11 +2176,11 @@
       </c>
       <c r="N4" s="3">
         <f>'10000160'!L3</f>
-        <v>0.56000000000000005</v>
+        <v>0.63000000000000012</v>
       </c>
       <c r="O4" s="3">
         <f>'10000160'!M3</f>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="P4" s="9"/>
       <c r="Q4" s="36"/>
@@ -2130,13 +2235,13 @@
         <f>'10000158'!B11</f>
         <v>46237</v>
       </c>
-      <c r="J5" s="6" t="str">
+      <c r="J5" s="6">
         <f>'10000158'!O3</f>
-        <v/>
-      </c>
-      <c r="K5" s="17">
+        <v>46237</v>
+      </c>
+      <c r="K5" s="17" t="str">
         <f ca="1">'10000158'!B12</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="L5" s="17" t="str">
         <f ca="1">'10000158'!P3</f>
@@ -2144,15 +2249,15 @@
       </c>
       <c r="M5" s="3">
         <f>'10000158'!K3</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N5" s="3">
         <f>'10000158'!L3</f>
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="O5" s="3">
         <f>'10000158'!M3</f>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="P5" s="9"/>
       <c r="AC5" s="3" t="str">
@@ -2202,7 +2307,7 @@
       </c>
       <c r="K6" s="17">
         <f ca="1">'10000170'!B12</f>
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L6" s="17" t="str">
         <f ca="1">'10000170'!P3</f>
@@ -2268,7 +2373,7 @@
       </c>
       <c r="K7" s="17">
         <f ca="1">'10000212'!B12</f>
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L7" s="17" t="str">
         <f ca="1">'10000212'!P3</f>
@@ -2334,7 +2439,7 @@
       </c>
       <c r="K8" s="17">
         <f ca="1">'10000263'!B12</f>
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="L8" s="17" t="str">
         <f ca="1">'10000263'!P3</f>
@@ -2400,7 +2505,7 @@
       </c>
       <c r="K9" s="17">
         <f ca="1">'10000288'!B12</f>
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="L9" s="17" t="str">
         <f ca="1">'10000288'!P3</f>
@@ -2466,7 +2571,7 @@
       </c>
       <c r="K10" s="17">
         <f ca="1">'10000437'!B12</f>
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="L10" s="17" t="str">
         <f ca="1">'10000437'!P3</f>
@@ -2532,7 +2637,7 @@
       </c>
       <c r="K11" s="17">
         <f ca="1">'10000591'!B12</f>
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L11" s="17" t="str">
         <f ca="1">'10000591'!P3</f>
@@ -2598,7 +2703,7 @@
       </c>
       <c r="K12" s="17">
         <f ca="1">'10000722'!B12</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L12" s="17" t="str">
         <f ca="1">'10000722'!P3</f>
@@ -2664,7 +2769,7 @@
       </c>
       <c r="K13" s="17">
         <f ca="1">'10001244'!B12</f>
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L13" s="17" t="str">
         <f ca="1">'10001244'!P3</f>
@@ -2682,25 +2787,75 @@
         <f>'10001244'!M3</f>
         <v>0</v>
       </c>
-      <c r="AC13" s="1"/>
+      <c r="AC13" s="3" t="str">
+        <f ca="1">'10001244'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="3"/>
-      <c r="AC14" s="1"/>
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6">
+        <f>'10001352'!B9</f>
+        <v>46238</v>
+      </c>
+      <c r="C14" s="26" t="str">
+        <f>'10001352'!B1</f>
+        <v>ID 205174291 - 10001352</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f>'10001352'!B2</f>
+        <v>Bulgaria</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f>'10001352'!B3</f>
+        <v>Tiberus</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f>'10001352'!B8</f>
+        <v>0 m. 3 mėn. 11 d.</v>
+      </c>
+      <c r="G14" s="7">
+        <f>'10001352'!B15</f>
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="3">
+        <f>'10001352'!B16</f>
+        <v>22.13</v>
+      </c>
+      <c r="I14" s="6">
+        <f>'10001352'!B11</f>
+        <v>46341</v>
+      </c>
+      <c r="J14" s="6" t="str">
+        <f>'10001352'!O3</f>
+        <v/>
+      </c>
+      <c r="K14" s="17">
+        <f ca="1">'10001352'!B12</f>
+        <v>103</v>
+      </c>
+      <c r="L14" s="17" t="str">
+        <f ca="1">'10001352'!P3</f>
+        <v/>
+      </c>
+      <c r="M14" s="3">
+        <f>'10001352'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <f>'10001352'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <f>'10001352'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="str">
+        <f ca="1">'10001352'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -2981,30 +3136,38 @@
     <mergeCell ref="U1:V1"/>
     <mergeCell ref="W1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="O3:O13 A3:N27">
-    <cfRule type="expression" dxfId="49" priority="17">
+  <conditionalFormatting sqref="A15:N27 A3:O14">
+    <cfRule type="expression" dxfId="55" priority="19">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="18">
+    <cfRule type="expression" dxfId="54" priority="20">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O14:O27">
-    <cfRule type="expression" dxfId="47" priority="19">
-      <formula>$AD14="+"</formula>
+  <conditionalFormatting sqref="O15:O27">
+    <cfRule type="expression" dxfId="53" priority="21">
+      <formula>$AD15="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="20">
-      <formula>AND($M14&gt;0,$H14=$M14)</formula>
+    <cfRule type="expression" dxfId="52" priority="22">
+      <formula>AND($M15&gt;0,$H15=$M15)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC12">
-    <cfRule type="expression" dxfId="45" priority="3">
+    <cfRule type="expression" dxfId="51" priority="5">
       <formula>$AC3="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC3:AC27">
-    <cfRule type="expression" dxfId="44" priority="4">
+  <conditionalFormatting sqref="AC3:AC12 AC15:AC27">
+    <cfRule type="expression" dxfId="50" priority="6">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC13:AC14">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$AC13="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>AND($M13&gt;0,$H13=$M13)</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3019,6 +3182,7 @@
     <hyperlink ref="C11" location="'10000591'!A1" display="'10000591'!A1" xr:uid="{7B47A2A7-BE3F-43BD-BB28-A42FD0488833}"/>
     <hyperlink ref="C12" location="'10000722'!A1" display="'10000722'!A1" xr:uid="{53AFE255-A743-4FED-8BCF-22069A94522F}"/>
     <hyperlink ref="C13" location="'10001244'!A1" display="'10001244'!A1" xr:uid="{FC30CDB7-344C-44CB-ACB0-7338CE7FF85C}"/>
+    <hyperlink ref="C14" location="'10001352'!A1" display="'10001352'!A1" xr:uid="{CAA6D28E-7838-4CCA-889F-481F0C1FFFCA}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="50" orientation="landscape" r:id="rId1"/>
@@ -3026,6 +3190,1348 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A9BB0F-4DAC-47C2-A73D-F62E2AA7D40E}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="41"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="42"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="42"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46041</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46041</v>
+      </c>
+      <c r="F3" s="17">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46007</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-21.49</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46072</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46072</v>
+      </c>
+      <c r="F4" s="17">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46041</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0.18000000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10">
+        <v>46100</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46100</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46072</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0.18000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10">
+        <v>46131</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46131</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46100</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10">
+        <v>46161</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46161</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46131</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0.18000000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>1 m. 0 mėn. 3 d.</v>
+      </c>
+      <c r="D8" s="10">
+        <v>46192</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46192</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46161</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46007</v>
+      </c>
+      <c r="D9" s="10">
+        <v>46222</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46222</v>
+      </c>
+      <c r="F9" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>46192</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0.18000000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46010</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46375</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="17">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>137</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="24"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3">
+        <v>21.49</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="25"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="25" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="23" priority="7">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="22" priority="8">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34AD5732-D270-469F-AE8D-DB41E9FD857B}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3475,7 +4981,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -4354,20 +5860,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="19" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="18" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4377,8 +5883,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AE231A-5892-4EFF-BD83-B2EFEC23A29B}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4514,31 +6023,31 @@
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.08</v>
-      </c>
-      <c r="N3" s="7" t="str">
+        <v>0.09</v>
+      </c>
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>6.1380931735038752E-2</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
+        <v>46237</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2" t="str">
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
@@ -4802,15 +6311,25 @@
       <c r="B11" s="6">
         <v>46237</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="D11" s="10">
+        <v>46237</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46237</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.01</v>
+      </c>
       <c r="J11" s="14"/>
       <c r="X11" s="6">
         <f t="shared" si="1"/>
@@ -4825,9 +6344,9 @@
       <c r="A12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="17" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -4841,11 +6360,11 @@
       <c r="J12" s="14"/>
       <c r="X12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46237</v>
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.050000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -5687,15 +7206,15 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -5706,20 +7225,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="15" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="14" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5729,7 +7248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA182266-9A58-49E8-A957-D70695644CFF}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5870,11 +7389,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.56000000000000005</v>
+        <v>0.63000000000000012</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -6154,15 +7673,25 @@
       <c r="B11" s="6">
         <v>46510</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="D11" s="10">
+        <v>46237</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46237</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.01</v>
+      </c>
       <c r="J11" s="14"/>
       <c r="X11" s="6">
         <f t="shared" si="1"/>
@@ -6179,7 +7708,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -6193,11 +7722,11 @@
       <c r="J12" s="14"/>
       <c r="X12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46237</v>
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -7043,11 +8572,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.56000000000000005</v>
+        <v>0.63000000000000012</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -7058,20 +8587,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="4" priority="8">
+    <cfRule type="expression" dxfId="10" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7081,7 +8610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BCFDB1-6048-4D44-8902-982713D3B194}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7222,11 +8751,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>4.24</v>
+        <v>4.78</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.39999999999999997</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -7506,15 +9035,25 @@
       <c r="B11" s="6">
         <v>46329</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="D11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46237</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.05</v>
+      </c>
       <c r="J11" s="14"/>
       <c r="X11" s="6">
         <f t="shared" si="1"/>
@@ -7531,7 +9070,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -7545,11 +9084,11 @@
       <c r="J12" s="14"/>
       <c r="X12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46237</v>
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.49000000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -8395,11 +9934,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>4.24</v>
+        <v>4.78</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.39999999999999997</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -8410,20 +9949,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8488,7 +10027,7 @@
       </c>
       <c r="F2" s="3">
         <f>SUM(B2:B35)</f>
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G2" s="3">
         <f>SUM(C2:C35)</f>
@@ -8500,7 +10039,7 @@
       </c>
       <c r="I2" s="3">
         <f>F2-G2</f>
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="K2" s="3">
         <f>B2*-1</f>
@@ -8706,13 +10245,21 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="A14" s="6">
+        <v>46238</v>
+      </c>
+      <c r="B14" s="3">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
       <c r="K14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -10013,14 +11560,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="28">
         <f>Overview!W3</f>
-        <v>305</v>
+        <v>315.60000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -10029,6 +11576,1281 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08D1685-29BB-4A41-AE19-A366E62834D1}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="41"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="42"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="42"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46280</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="17" t="str">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46238</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-22.13</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46310</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10">
+        <v>46341</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="17" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 3 mėn. 11 d.</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46238</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46234</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46341</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="17">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>103</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="24"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3">
+        <v>22.13</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="25"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C677B129-A21F-4F7E-842A-943A1C9A9BD5}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10395,7 +13217,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -11274,20 +14096,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="49" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="2">
+    <cfRule type="expression" dxfId="48" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="41" priority="3">
+    <cfRule type="expression" dxfId="47" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="40" priority="4">
+    <cfRule type="expression" dxfId="46" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11297,7 +14119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3DE005-D575-41AB-BBD1-8242CE6C9813}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11687,7 +14509,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -12566,20 +15388,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="2">
+    <cfRule type="expression" dxfId="44" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="37" priority="3">
+    <cfRule type="expression" dxfId="43" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="42" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12589,7 +15411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040679F3-0213-4B39-8DBC-0E51B0F9A058}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12989,7 +15811,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -13868,20 +16690,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="41" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="2">
+    <cfRule type="expression" dxfId="40" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="33" priority="9">
+    <cfRule type="expression" dxfId="39" priority="9">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="32" priority="10">
+    <cfRule type="expression" dxfId="38" priority="10">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13891,7 +16713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA72114-51C2-4C21-92BC-1004D7B25863}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14300,7 +17122,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -15179,20 +18001,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="37" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="2">
+    <cfRule type="expression" dxfId="36" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="35" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="28" priority="8">
+    <cfRule type="expression" dxfId="34" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15202,7 +18024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759D5263-CE33-4927-93AA-6232274D84F9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15622,7 +18444,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -16501,20 +19323,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="2">
+    <cfRule type="expression" dxfId="32" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="25" priority="7">
+    <cfRule type="expression" dxfId="31" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="24" priority="8">
+    <cfRule type="expression" dxfId="30" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16524,7 +19346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B61398-82DC-4A18-83BA-B3E07706D6C6}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16944,7 +19766,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -17823,1362 +20645,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="28" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="21" priority="7">
+    <cfRule type="expression" dxfId="27" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="20" priority="8">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A9BB0F-4DAC-47C2-A73D-F62E2AA7D40E}">
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="10">
-        <v>46041</v>
-      </c>
-      <c r="E3" s="10">
-        <v>46041</v>
-      </c>
-      <c r="F3" s="17">
-        <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="13"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46007</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-21.49</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="10">
-        <v>46072</v>
-      </c>
-      <c r="E4" s="10">
-        <v>46072</v>
-      </c>
-      <c r="F4" s="17">
-        <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46041</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="10">
-        <v>46100</v>
-      </c>
-      <c r="E5" s="10">
-        <v>46100</v>
-      </c>
-      <c r="F5" s="17">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.18</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46072</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="10">
-        <v>46131</v>
-      </c>
-      <c r="E6" s="10">
-        <v>46131</v>
-      </c>
-      <c r="F6" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46100</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="10">
-        <v>46161</v>
-      </c>
-      <c r="E7" s="10">
-        <v>46161</v>
-      </c>
-      <c r="F7" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46131</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>1 m. 0 mėn. 3 d.</v>
-      </c>
-      <c r="D8" s="10">
-        <v>46192</v>
-      </c>
-      <c r="E8" s="6">
-        <v>46192</v>
-      </c>
-      <c r="F8" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>46161</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46007</v>
-      </c>
-      <c r="D9" s="10">
-        <v>46222</v>
-      </c>
-      <c r="E9" s="6">
-        <v>46222</v>
-      </c>
-      <c r="F9" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.19</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>46192</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46010</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>46222</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46375</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="14"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="17">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>143</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="14"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
-      <c r="N13" s="13"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="14"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.11</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="3">
-        <v>21.49</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="14"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="14"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="14"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="14"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="14"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="14"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="14"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="14"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="14"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="14"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="14"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="14"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="14"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="14"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="14"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="14"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="19" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="17" priority="7">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="26" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/excel/Afranga.xlsx
+++ b/excel/Afranga.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Afranga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Afranga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918EEC03-F886-49BC-9D7C-E0B9967570FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A36710-AEB7-416A-B209-B316617BD33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="10001352" sheetId="36" r:id="rId3"/>
-    <sheet name="10001244" sheetId="35" r:id="rId4"/>
-    <sheet name="10000722" sheetId="34" r:id="rId5"/>
-    <sheet name="10000591" sheetId="33" r:id="rId6"/>
-    <sheet name="10000437" sheetId="32" r:id="rId7"/>
-    <sheet name="10000288" sheetId="31" r:id="rId8"/>
-    <sheet name="10000263" sheetId="30" r:id="rId9"/>
-    <sheet name="10000212" sheetId="29" r:id="rId10"/>
-    <sheet name="10000170" sheetId="28" r:id="rId11"/>
-    <sheet name="10000158" sheetId="27" r:id="rId12"/>
-    <sheet name="10000160" sheetId="26" r:id="rId13"/>
-    <sheet name="10000159" sheetId="24" r:id="rId14"/>
+    <sheet name="10001457" sheetId="37" r:id="rId3"/>
+    <sheet name="10001352" sheetId="36" r:id="rId4"/>
+    <sheet name="10001244" sheetId="35" r:id="rId5"/>
+    <sheet name="10000722" sheetId="34" r:id="rId6"/>
+    <sheet name="10000591" sheetId="33" r:id="rId7"/>
+    <sheet name="10000437" sheetId="32" r:id="rId8"/>
+    <sheet name="10000288" sheetId="31" r:id="rId9"/>
+    <sheet name="10000263" sheetId="30" r:id="rId10"/>
+    <sheet name="10000212" sheetId="29" r:id="rId11"/>
+    <sheet name="10000170" sheetId="28" r:id="rId12"/>
+    <sheet name="10000158" sheetId="27" r:id="rId13"/>
+    <sheet name="10000160" sheetId="26" r:id="rId14"/>
+    <sheet name="10000159" sheetId="24" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="62">
   <si>
     <t>Paskola</t>
   </si>
@@ -231,10 +232,10 @@
     <t>Viso</t>
   </si>
   <si>
-    <t>2026-08-03</t>
+    <t>ID 205174291 - 10001352</t>
   </si>
   <si>
-    <t>ID 205174291 - 10001352</t>
+    <t>ID 205174291 - 10001457</t>
   </si>
 </sst>
 </file>
@@ -245,7 +246,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\.mm\.dd;@"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +277,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="186"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -398,7 +406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -494,6 +502,15 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -529,7 +546,21 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="58">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -540,7 +571,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -956,7 +987,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{275BD4ED-4B57-4162-83D2-854F97D2036F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB075466-8F55-4EDF-A6FB-15B890F93797}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1012,7 +1043,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED2ECCA0-80A3-426C-A608-F4925BC22406}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7DEFBA9-93E5-4EF0-9E7B-D6DF25DCCADD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1068,6 +1099,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED2ECCA0-80A3-426C-A608-F4925BC22406}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F1463A4-8800-48EC-B2CB-1A3F6A0C6A19}"/>
             </a:ext>
           </a:extLst>
@@ -1103,7 +1190,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1180,7 +1267,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E90775C4-BAB6-4D13-B640-C0DF738ECBD6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{275BD4ED-4B57-4162-83D2-854F97D2036F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1236,7 +1323,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCBE527D-4A23-4E4A-AC7E-1AFBA1CAB55A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E90775C4-BAB6-4D13-B640-C0DF738ECBD6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1292,7 +1379,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EE4D48B-03EB-4D83-A46B-315D6745E732}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCBE527D-4A23-4E4A-AC7E-1AFBA1CAB55A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1348,7 +1435,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47FF4319-555E-4F69-8EBB-76B3297F2074}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EE4D48B-03EB-4D83-A46B-315D6745E732}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1404,7 +1491,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A793C6-D2B0-460B-B330-1B6E7FE7CDFC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47FF4319-555E-4F69-8EBB-76B3297F2074}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1460,7 +1547,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D16E9C-0AB8-45AB-928F-FA2477F6577D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3A793C6-D2B0-460B-B330-1B6E7FE7CDFC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1516,7 +1603,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E47B75D7-93D2-48E8-AD9A-78030D97E09E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D16E9C-0AB8-45AB-928F-FA2477F6577D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1572,7 +1659,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7DEFBA9-93E5-4EF0-9E7B-D6DF25DCCADD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E47B75D7-93D2-48E8-AD9A-78030D97E09E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1887,43 +1974,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40" t="s">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43" t="s">
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="Q1" s="44" t="s">
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="Q1" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="44" t="s">
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="V1" s="46"/>
-      <c r="W1" s="40" t="s">
+      <c r="V1" s="49"/>
+      <c r="W1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
       <c r="AA1" s="4" t="s">
         <v>39</v>
       </c>
@@ -2054,7 +2141,7 @@
       </c>
       <c r="K3" s="17">
         <f ca="1">'10000159'!B12</f>
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="L3" s="17" t="str">
         <f ca="1">'10000159'!P3</f>
@@ -2079,7 +2166,7 @@
       </c>
       <c r="R3" s="32">
         <f>SUM(H3:H100)-U3</f>
-        <v>315.59999999999997</v>
+        <v>317.40999999999997</v>
       </c>
       <c r="S3" s="33">
         <f>Pinigai!H2</f>
@@ -2091,31 +2178,31 @@
       </c>
       <c r="U3" s="32">
         <f>SUM(M3:M100)</f>
-        <v>10</v>
+        <v>31.82</v>
       </c>
       <c r="V3" s="32">
         <f>SUM(N3:N100)-AA3</f>
-        <v>13.73</v>
+        <v>15.54</v>
       </c>
       <c r="W3" s="32">
         <f>Q3+V3+S3</f>
-        <v>315.60000000000002</v>
+        <v>317.41000000000003</v>
       </c>
       <c r="X3" s="32">
         <f>W3-Q3</f>
-        <v>15.600000000000023</v>
+        <v>17.410000000000025</v>
       </c>
       <c r="Y3" s="35">
         <f>(W3-Q3)/Q3</f>
-        <v>5.2000000000000074E-2</v>
+        <v>5.8033333333333416E-2</v>
       </c>
       <c r="Z3" s="35">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>9.646490216255188E-2</v>
+        <v>9.4554528594017001E-2</v>
       </c>
       <c r="AA3" s="32">
         <f>SUM(O3:O100)</f>
-        <v>1.6000000000000005</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" s="3" t="str">
         <f ca="1">'10000159'!Z3</f>
@@ -2164,7 +2251,7 @@
       </c>
       <c r="K4" s="17">
         <f ca="1">'10000160'!B12</f>
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="L4" s="17" t="str">
         <f ca="1">'10000160'!P3</f>
@@ -2307,7 +2394,7 @@
       </c>
       <c r="K6" s="17">
         <f ca="1">'10000170'!B12</f>
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="L6" s="17" t="str">
         <f ca="1">'10000170'!P3</f>
@@ -2319,11 +2406,11 @@
       </c>
       <c r="N6" s="3">
         <f>'10000170'!L3</f>
-        <v>3.6500000000000004</v>
+        <v>4.12</v>
       </c>
       <c r="O6" s="3">
         <f>'10000170'!M3</f>
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="P6" s="9"/>
       <c r="AC6" s="3" t="str">
@@ -2373,7 +2460,7 @@
       </c>
       <c r="K7" s="17">
         <f ca="1">'10000212'!B12</f>
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="L7" s="17" t="str">
         <f ca="1">'10000212'!P3</f>
@@ -2385,11 +2472,11 @@
       </c>
       <c r="N7" s="3">
         <f>'10000212'!L3</f>
-        <v>1.3599999999999999</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="O7" s="3">
         <f>'10000212'!M3</f>
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="P7" s="9"/>
       <c r="AC7" s="3" t="str">
@@ -2439,7 +2526,7 @@
       </c>
       <c r="K8" s="17">
         <f ca="1">'10000263'!B12</f>
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="L8" s="17" t="str">
         <f ca="1">'10000263'!P3</f>
@@ -2451,11 +2538,11 @@
       </c>
       <c r="N8" s="3">
         <f>'10000263'!L3</f>
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="O8" s="3">
         <f>'10000263'!M3</f>
-        <v>0.11000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="P8" s="9"/>
       <c r="AC8" s="3" t="str">
@@ -2505,7 +2592,7 @@
       </c>
       <c r="K9" s="17">
         <f ca="1">'10000288'!B12</f>
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="L9" s="17" t="str">
         <f ca="1">'10000288'!P3</f>
@@ -2517,11 +2604,11 @@
       </c>
       <c r="N9" s="3">
         <f>'10000288'!L3</f>
-        <v>1.1000000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="O9" s="3">
         <f>'10000288'!M3</f>
-        <v>0.1</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="P9" s="9"/>
       <c r="AC9" s="3" t="str">
@@ -2571,7 +2658,7 @@
       </c>
       <c r="K10" s="17">
         <f ca="1">'10000437'!B12</f>
-        <v>967</v>
+        <v>940</v>
       </c>
       <c r="L10" s="17" t="str">
         <f ca="1">'10000437'!P3</f>
@@ -2583,11 +2670,11 @@
       </c>
       <c r="N10" s="3">
         <f>'10000437'!L3</f>
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="O10" s="3">
         <f>'10000437'!M3</f>
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="P10" s="9"/>
       <c r="AC10" s="3" t="str">
@@ -2637,7 +2724,7 @@
       </c>
       <c r="K11" s="17">
         <f ca="1">'10000591'!B12</f>
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="L11" s="17" t="str">
         <f ca="1">'10000591'!P3</f>
@@ -2649,11 +2736,11 @@
       </c>
       <c r="N11" s="3">
         <f>'10000591'!L3</f>
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="O11" s="3">
         <f>'10000591'!M3</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="P11" s="9"/>
       <c r="AC11" s="3" t="str">
@@ -2697,13 +2784,13 @@
         <f>'10000722'!B11</f>
         <v>46262</v>
       </c>
-      <c r="J12" s="6" t="str">
+      <c r="J12" s="6">
         <f>'10000722'!O3</f>
-        <v/>
-      </c>
-      <c r="K12" s="17">
+        <v>46262</v>
+      </c>
+      <c r="K12" s="17" t="str">
         <f ca="1">'10000722'!B12</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="L12" s="17" t="str">
         <f ca="1">'10000722'!P3</f>
@@ -2711,15 +2798,15 @@
       </c>
       <c r="M12" s="3">
         <f>'10000722'!K3</f>
-        <v>0</v>
+        <v>21.82</v>
       </c>
       <c r="N12" s="3">
         <f>'10000722'!L3</f>
-        <v>0.38</v>
+        <v>0.57000000000000006</v>
       </c>
       <c r="O12" s="3">
         <f>'10000722'!M3</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="P12" s="9"/>
       <c r="AC12" s="3" t="str">
@@ -2769,7 +2856,7 @@
       </c>
       <c r="K13" s="17">
         <f ca="1">'10001244'!B12</f>
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="L13" s="17" t="str">
         <f ca="1">'10001244'!P3</f>
@@ -2781,11 +2868,11 @@
       </c>
       <c r="N13" s="3">
         <f>'10001244'!L3</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="O13" s="3">
         <f>'10001244'!M3</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AC13" s="3" t="str">
         <f ca="1">'10001244'!Z3</f>
@@ -2834,7 +2921,7 @@
       </c>
       <c r="K14" s="17">
         <f ca="1">'10001352'!B12</f>
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="L14" s="17" t="str">
         <f ca="1">'10001352'!P3</f>
@@ -2858,22 +2945,69 @@
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="3"/>
-      <c r="AC15" s="1"/>
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6">
+        <f>'10001457'!B9</f>
+        <v>46263</v>
+      </c>
+      <c r="C15" s="26" t="str">
+        <f>'10001457'!B1</f>
+        <v>ID 205174291 - 10001457</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f>'10001457'!B2</f>
+        <v>Bulgaria</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <f>'10001457'!B3</f>
+        <v>Tiberus</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f>'10001457'!B8</f>
+        <v>1 m. 0 mėn. 17 d.</v>
+      </c>
+      <c r="G15" s="7">
+        <f>'10001457'!B15</f>
+        <v>0.11</v>
+      </c>
+      <c r="H15" s="3">
+        <f>'10001457'!B16</f>
+        <v>23.63</v>
+      </c>
+      <c r="I15" s="6">
+        <f>'10001457'!B11</f>
+        <v>46645</v>
+      </c>
+      <c r="J15" s="6" t="str">
+        <f>'10001457'!O3</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f ca="1">'10001457'!B12</f>
+        <v>380</v>
+      </c>
+      <c r="L15" s="17" t="str">
+        <f ca="1">'10001457'!P3</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>'10001457'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <f>'10001457'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <f>'10001457'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="str">
+        <f ca="1">'10001457'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -2945,16 +3079,16 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="3"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-      <c r="S19" s="37"/>
-      <c r="T19" s="37"/>
-      <c r="U19" s="37"/>
-      <c r="V19" s="37"/>
-      <c r="W19" s="37"/>
-      <c r="X19" s="37"/>
-      <c r="Y19" s="37"/>
-      <c r="Z19" s="37"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="40"/>
+      <c r="Y19" s="40"/>
+      <c r="Z19" s="40"/>
       <c r="AA19" s="8"/>
       <c r="AC19" s="1"/>
     </row>
@@ -3136,38 +3270,30 @@
     <mergeCell ref="U1:V1"/>
     <mergeCell ref="W1:Z1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A15:N27 A3:O14">
-    <cfRule type="expression" dxfId="55" priority="19">
+  <conditionalFormatting sqref="A16:N27 A3:O15">
+    <cfRule type="expression" dxfId="57" priority="19">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="20">
+    <cfRule type="expression" dxfId="56" priority="20">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O15:O27">
-    <cfRule type="expression" dxfId="53" priority="21">
-      <formula>$AD15="+"</formula>
+  <conditionalFormatting sqref="O16:O27">
+    <cfRule type="expression" dxfId="55" priority="21">
+      <formula>$AD16="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="22">
-      <formula>AND($M15&gt;0,$H15=$M15)</formula>
+    <cfRule type="expression" dxfId="54" priority="22">
+      <formula>AND($M16&gt;0,$H16=$M16)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC3:AC12">
-    <cfRule type="expression" dxfId="51" priority="5">
+  <conditionalFormatting sqref="AC3:AC15">
+    <cfRule type="expression" dxfId="53" priority="1">
       <formula>$AC3="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC3:AC12 AC15:AC27">
-    <cfRule type="expression" dxfId="50" priority="6">
+  <conditionalFormatting sqref="AC3:AC27">
+    <cfRule type="expression" dxfId="52" priority="2">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC13:AC14">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$AC13="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND($M13&gt;0,$H13=$M13)</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3183,6 +3309,7 @@
     <hyperlink ref="C12" location="'10000722'!A1" display="'10000722'!A1" xr:uid="{53AFE255-A743-4FED-8BCF-22069A94522F}"/>
     <hyperlink ref="C13" location="'10001244'!A1" display="'10001244'!A1" xr:uid="{FC30CDB7-344C-44CB-ACB0-7338CE7FF85C}"/>
     <hyperlink ref="C14" location="'10001352'!A1" display="'10001352'!A1" xr:uid="{CAA6D28E-7838-4CCA-889F-481F0C1FFFCA}"/>
+    <hyperlink ref="C15" location="'10001457'!A1" display="'10001457'!A1" xr:uid="{5C3D8390-547B-41DC-8956-6CBD535AD21C}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="50" orientation="landscape" r:id="rId1"/>
@@ -3190,6 +3317,1350 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B61398-82DC-4A18-83BA-B3E07706D6C6}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46096</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46096</v>
+      </c>
+      <c r="F3" s="17">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>1.18</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0.13</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46042</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-21.2</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46127</v>
+      </c>
+      <c r="E4" s="10">
+        <v>46127</v>
+      </c>
+      <c r="F4" s="17">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46096</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10">
+        <v>46157</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46157</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>46127</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10">
+        <v>46188</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46188</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>46157</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10">
+        <v>46218</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46218</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>46188</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>1 m. 0 mėn. 26 d.</v>
+      </c>
+      <c r="D8" s="10">
+        <v>46249</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46249</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>46218</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46042</v>
+      </c>
+      <c r="D9" s="10">
+        <v>46280</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>46249</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46045</v>
+      </c>
+      <c r="D10" s="10">
+        <v>46310</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46433</v>
+      </c>
+      <c r="D11" s="10">
+        <v>46341</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="17">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>168</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46371</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10">
+        <v>46402</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="24"/>
+      <c r="D14" s="10">
+        <v>46433</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3">
+        <v>21.2</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="25"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>1.18</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0.13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="27" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="25" priority="7">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="24" priority="8">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A9BB0F-4DAC-47C2-A73D-F62E2AA7D40E}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3216,29 +4687,29 @@
       <c r="B1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3330,11 +4801,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.3599999999999999</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -3578,15 +5049,25 @@
       <c r="B10" s="6">
         <v>46010</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="D10" s="10">
+        <v>46253</v>
+      </c>
+      <c r="E10" s="6">
+        <v>46253</v>
+      </c>
+      <c r="F10" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.02</v>
+      </c>
       <c r="J10" s="14"/>
       <c r="X10" s="6">
         <f t="shared" si="1"/>
@@ -3604,7 +5085,9 @@
       <c r="B11" s="6">
         <v>46375</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="10">
+        <v>46284</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="17" t="str">
         <f t="shared" si="0"/>
@@ -3616,11 +5099,11 @@
       <c r="J11" s="14"/>
       <c r="X11" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46253</v>
       </c>
       <c r="Y11" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.18000000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -3629,9 +5112,11 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>137</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>110</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46314</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -3653,7 +5138,9 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
+      <c r="D13" s="10">
+        <v>46345</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -3676,7 +5163,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <v>46375</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
         <f t="shared" si="0"/>
@@ -4493,11 +5982,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.3599999999999999</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -4508,20 +5997,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="23" priority="7">
+    <cfRule type="expression" dxfId="21" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="22" priority="8">
+    <cfRule type="expression" dxfId="20" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4531,7 +6020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34AD5732-D270-469F-AE8D-DB41E9FD857B}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4558,29 +6047,29 @@
       <c r="B1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -4672,11 +6161,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>3.6500000000000004</v>
+        <v>4.12</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -4956,15 +6445,25 @@
       <c r="B11" s="6">
         <v>46340</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="D11" s="10">
+        <v>46248</v>
+      </c>
+      <c r="E11" s="6">
+        <v>46248</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.47</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.05</v>
+      </c>
       <c r="J11" s="14"/>
       <c r="X11" s="6">
         <f t="shared" si="1"/>
@@ -4981,9 +6480,11 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>102</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46279</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -4995,17 +6496,19 @@
       <c r="J12" s="14"/>
       <c r="X12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46248</v>
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
+      <c r="D13" s="10">
+        <v>46309</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -5028,7 +6531,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <v>46340</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
         <f t="shared" si="0"/>
@@ -5845,11 +7350,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>3.6500000000000004</v>
+        <v>4.12</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -5860,20 +7365,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="19" priority="7">
+    <cfRule type="expression" dxfId="17" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="18" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5883,7 +7388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AE231A-5892-4EFF-BD83-B2EFEC23A29B}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5913,29 +7418,29 @@
       <c r="B1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7225,20 +8730,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="14" priority="8">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7248,7 +8753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA182266-9A58-49E8-A957-D70695644CFF}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7275,29 +8780,29 @@
       <c r="B1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7708,9 +9213,11 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>272</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>245</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46268</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7732,7 +9239,9 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
+      <c r="D13" s="10">
+        <v>46298</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7755,7 +9264,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <v>46329</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7781,7 +9292,9 @@
       <c r="B15" s="12">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="10">
+        <v>46359</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7814,7 +9327,9 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="D16" s="10"/>
+      <c r="D16" s="10">
+        <v>46390</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7841,7 +9356,9 @@
       </c>
     </row>
     <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
+      <c r="D17" s="10">
+        <v>46421</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7861,7 +9378,9 @@
       </c>
     </row>
     <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
+      <c r="D18" s="10">
+        <v>46449</v>
+      </c>
       <c r="E18" s="6"/>
       <c r="F18" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7881,7 +9400,9 @@
       </c>
     </row>
     <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
+      <c r="D19" s="10">
+        <v>46480</v>
+      </c>
       <c r="E19" s="6"/>
       <c r="F19" s="17" t="str">
         <f t="shared" si="0"/>
@@ -7901,7 +9422,9 @@
       </c>
     </row>
     <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
+      <c r="D20" s="10">
+        <v>46510</v>
+      </c>
       <c r="E20" s="6"/>
       <c r="F20" s="17" t="str">
         <f t="shared" si="0"/>
@@ -8587,20 +10110,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="11" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8610,7 +10133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BCFDB1-6048-4D44-8902-982713D3B194}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8637,29 +10160,29 @@
       <c r="B1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -9035,8 +10558,8 @@
       <c r="B11" s="6">
         <v>46329</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>60</v>
+      <c r="D11" s="37">
+        <v>46237</v>
       </c>
       <c r="E11" s="6">
         <v>46237</v>
@@ -9070,9 +10593,11 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>91</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>64</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46268</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -9094,7 +10619,9 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
+      <c r="D13" s="10">
+        <v>46298</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -9117,7 +10644,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <v>46329</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
         <f t="shared" si="0"/>
@@ -9948,21 +11477,22 @@
     <mergeCell ref="K1:Q1"/>
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11560,14 +13090,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46238</v>
+        <v>46265</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="28">
         <f>Overview!W3</f>
-        <v>315.60000000000002</v>
+        <v>317.41000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -11576,6 +13106,1277 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86CC066A-7CFC-4675-A152-C5BCCBB3FD23}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" s="39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46310</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="17" t="str">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46263</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-23.63</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="9"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="17" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="9"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="9"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>1 m. 0 mėn. 17 d.</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="9"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46263</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46263</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46645</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="17">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>380</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="24"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3">
+        <v>23.63</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="10"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="10"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="10"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="10"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="10"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="10"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="10"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="10"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="10"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="10"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="10"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="10"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="10"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="10"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="10"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="10"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="10"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="10"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="9"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="25"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E08D1685-29BB-4A41-AE19-A366E62834D1}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11600,31 +14401,31 @@
         <v>18</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -11948,7 +14749,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -12827,20 +15628,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="50" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="49" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="48" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12850,7 +15651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C677B129-A21F-4F7E-842A-943A1C9A9BD5}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12877,29 +15678,29 @@
       <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -12965,15 +15766,25 @@
       <c r="B3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="17" t="str">
+      <c r="D3" s="10">
+        <v>46249</v>
+      </c>
+      <c r="E3" s="10">
+        <v>46249</v>
+      </c>
+      <c r="F3" s="17">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.02</v>
+      </c>
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
@@ -12981,11 +15792,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -13024,7 +15835,9 @@
       <c r="B4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10">
+        <v>46280</v>
+      </c>
       <c r="E4" s="10"/>
       <c r="F4" s="17"/>
       <c r="G4" s="3"/>
@@ -13033,17 +15846,19 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46249</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>0.21000000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="10"/>
+      <c r="D5" s="10">
+        <v>46310</v>
+      </c>
       <c r="E5" s="10"/>
       <c r="F5" s="17" t="str">
         <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
@@ -13217,7 +16032,7 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -14081,11 +16896,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -14096,20 +16911,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="2">
+    <cfRule type="expression" dxfId="46" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="47" priority="3">
+    <cfRule type="expression" dxfId="45" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="46" priority="4">
+    <cfRule type="expression" dxfId="44" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14119,8 +16934,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3DE005-D575-41AB-BBD1-8242CE6C9813}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14146,29 +16964,29 @@
       <c r="B1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -14256,31 +17074,31 @@
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>21.82</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.38</v>
+        <v>0.57000000000000006</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.04</v>
-      </c>
-      <c r="N3" s="7" t="str">
+        <v>0.06</v>
+      </c>
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>9.1536757349967968E-2</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
+        <v>46262</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2" t="str">
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
@@ -14335,15 +17153,25 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="D5" s="10">
+        <v>46262</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46262</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>21.82</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.02</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -14369,11 +17197,11 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46262</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21.990000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -14507,9 +17335,9 @@
       <c r="A12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="17" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -15369,15 +18197,15 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>21.82</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="4">SUM(H3:H52)</f>
-        <v>0.38</v>
+        <v>0.57000000000000006</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="4"/>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>
@@ -15388,20 +18216,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="2">
+    <cfRule type="expression" dxfId="42" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="43" priority="3">
+    <cfRule type="expression" dxfId="41" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="42" priority="4">
+    <cfRule type="expression" dxfId="40" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15411,7 +18239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040679F3-0213-4B39-8DBC-0E51B0F9A058}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15438,29 +18266,29 @@
       <c r="B1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -15552,11 +18380,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -15659,15 +18487,25 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
+      <c r="D6" s="10">
+        <v>46262</v>
+      </c>
+      <c r="E6" s="10">
+        <v>46262</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.02</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
@@ -15681,7 +18519,9 @@
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="D7" s="10"/>
+      <c r="D7" s="10">
+        <v>46293</v>
+      </c>
       <c r="E7" s="10"/>
       <c r="F7" s="17" t="str">
         <f t="shared" si="0"/>
@@ -15693,11 +18533,11 @@
       <c r="J7" s="14"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46262</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -15708,7 +18548,9 @@
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
         <v>1 m. 0 mėn. 7 d.</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="10">
+        <v>46323</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="17" t="str">
         <f t="shared" si="0"/>
@@ -15734,7 +18576,9 @@
       <c r="B9" s="6">
         <v>46133</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="10">
+        <v>46354</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="17" t="str">
         <f t="shared" si="0"/>
@@ -15760,7 +18604,9 @@
       <c r="B10" s="6">
         <v>46137</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="10">
+        <v>46384</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="17" t="str">
         <f t="shared" si="0"/>
@@ -15786,7 +18632,9 @@
       <c r="B11" s="6">
         <v>46505</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="10">
+        <v>46415</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="17" t="str">
         <f t="shared" si="0"/>
@@ -15811,9 +18659,11 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>267</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>240</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46446</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -15835,7 +18685,9 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
+      <c r="D13" s="10">
+        <v>46474</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -15858,7 +18710,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <v>46505</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
         <f t="shared" si="0"/>
@@ -16675,11 +19529,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -16690,20 +19544,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="39" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="2">
+    <cfRule type="expression" dxfId="38" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="39" priority="9">
+    <cfRule type="expression" dxfId="37" priority="9">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="38" priority="10">
+    <cfRule type="expression" dxfId="36" priority="10">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16713,7 +19567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA72114-51C2-4C21-92BC-1004D7B25863}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16740,29 +19594,29 @@
       <c r="B1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -16854,11 +19708,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -16961,10 +19815,10 @@
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="D6" s="10">
-        <v>46211</v>
+        <v>46231</v>
       </c>
       <c r="E6" s="10">
-        <v>46211</v>
+        <v>46231</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="0"/>
@@ -16992,19 +19846,29 @@
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="D7" s="10">
+        <v>46262</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46262</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.03</v>
+      </c>
       <c r="J7" s="14"/>
       <c r="X7" s="6">
         <f t="shared" si="1"/>
-        <v>46211</v>
+        <v>46231</v>
       </c>
       <c r="Y7" s="3">
         <f t="shared" si="2"/>
@@ -17019,7 +19883,9 @@
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
         <v>3 m. 0 mėn. 8 d.</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="10">
+        <v>46293</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17031,11 +19897,11 @@
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46262</v>
       </c>
       <c r="Y8" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -17045,7 +19911,9 @@
       <c r="B9" s="6">
         <v>46101</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="10">
+        <v>46323</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17071,7 +19939,9 @@
       <c r="B10" s="6">
         <v>46104</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="10">
+        <v>46354</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17097,7 +19967,9 @@
       <c r="B11" s="6">
         <v>47205</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="10">
+        <v>46384</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17122,9 +19994,11 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>967</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>940</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46415</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17146,7 +20020,9 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
+      <c r="D13" s="10">
+        <v>46446</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17169,7 +20045,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <v>46474</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17195,7 +20073,9 @@
       <c r="B15" s="7">
         <v>0.16</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="10">
+        <v>46505</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17228,7 +20108,9 @@
       <c r="B16" s="3">
         <v>22.16</v>
       </c>
-      <c r="D16" s="10"/>
+      <c r="D16" s="10">
+        <v>46535</v>
+      </c>
       <c r="E16" s="6"/>
       <c r="F16" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17255,7 +20137,9 @@
       </c>
     </row>
     <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
+      <c r="D17" s="10">
+        <v>46566</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17275,7 +20159,9 @@
       </c>
     </row>
     <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
+      <c r="D18" s="10">
+        <v>46596</v>
+      </c>
       <c r="E18" s="6"/>
       <c r="F18" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17295,7 +20181,9 @@
       </c>
     </row>
     <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
+      <c r="D19" s="10">
+        <v>46627</v>
+      </c>
       <c r="E19" s="6"/>
       <c r="F19" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17315,7 +20203,9 @@
       </c>
     </row>
     <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
+      <c r="D20" s="10">
+        <v>46658</v>
+      </c>
       <c r="E20" s="6"/>
       <c r="F20" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17335,7 +20225,9 @@
       </c>
     </row>
     <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
+      <c r="D21" s="10">
+        <v>46688</v>
+      </c>
       <c r="E21" s="6"/>
       <c r="F21" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17355,7 +20247,9 @@
       </c>
     </row>
     <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
+      <c r="D22" s="10">
+        <v>46719</v>
+      </c>
       <c r="E22" s="6"/>
       <c r="F22" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17375,7 +20269,9 @@
       </c>
     </row>
     <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
+      <c r="D23" s="10">
+        <v>46749</v>
+      </c>
       <c r="E23" s="6"/>
       <c r="F23" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17395,7 +20291,9 @@
       </c>
     </row>
     <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
+      <c r="D24" s="10">
+        <v>46780</v>
+      </c>
       <c r="E24" s="6"/>
       <c r="F24" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17415,7 +20313,9 @@
       </c>
     </row>
     <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
+      <c r="D25" s="10">
+        <v>46811</v>
+      </c>
       <c r="E25" s="6"/>
       <c r="F25" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17435,7 +20335,9 @@
       </c>
     </row>
     <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
+      <c r="D26" s="10">
+        <v>46840</v>
+      </c>
       <c r="E26" s="6"/>
       <c r="F26" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17455,7 +20357,9 @@
       </c>
     </row>
     <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
+      <c r="D27" s="10">
+        <v>46871</v>
+      </c>
       <c r="E27" s="6"/>
       <c r="F27" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17475,7 +20379,9 @@
       </c>
     </row>
     <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
+      <c r="D28" s="10">
+        <v>46901</v>
+      </c>
       <c r="E28" s="6"/>
       <c r="F28" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17495,7 +20401,9 @@
       </c>
     </row>
     <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
+      <c r="D29" s="10">
+        <v>46932</v>
+      </c>
       <c r="E29" s="6"/>
       <c r="F29" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17515,7 +20423,9 @@
       </c>
     </row>
     <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
+      <c r="D30" s="10">
+        <v>46962</v>
+      </c>
       <c r="E30" s="6"/>
       <c r="F30" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17535,7 +20445,9 @@
       </c>
     </row>
     <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
+      <c r="D31" s="10">
+        <v>46993</v>
+      </c>
       <c r="E31" s="6"/>
       <c r="F31" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17555,7 +20467,9 @@
       </c>
     </row>
     <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
+      <c r="D32" s="10">
+        <v>47024</v>
+      </c>
       <c r="E32" s="6"/>
       <c r="F32" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17575,7 +20489,9 @@
       </c>
     </row>
     <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
+      <c r="D33" s="10">
+        <v>47054</v>
+      </c>
       <c r="E33" s="6"/>
       <c r="F33" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17595,7 +20511,9 @@
       </c>
     </row>
     <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
+      <c r="D34" s="10">
+        <v>47085</v>
+      </c>
       <c r="E34" s="6"/>
       <c r="F34" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17615,7 +20533,9 @@
       </c>
     </row>
     <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
+      <c r="D35" s="10">
+        <v>47115</v>
+      </c>
       <c r="E35" s="6"/>
       <c r="F35" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17635,7 +20555,9 @@
       </c>
     </row>
     <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
+      <c r="D36" s="10">
+        <v>47146</v>
+      </c>
       <c r="E36" s="6"/>
       <c r="F36" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17655,7 +20577,9 @@
       </c>
     </row>
     <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
+      <c r="D37" s="10">
+        <v>47177</v>
+      </c>
       <c r="E37" s="6"/>
       <c r="F37" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17675,7 +20599,9 @@
       </c>
     </row>
     <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
+      <c r="D38" s="10">
+        <v>47205</v>
+      </c>
       <c r="E38" s="6"/>
       <c r="F38" s="17" t="str">
         <f t="shared" si="0"/>
@@ -17986,11 +20912,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -18001,20 +20927,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="2">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="35" priority="7">
+    <cfRule type="expression" dxfId="33" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="34" priority="8">
+    <cfRule type="expression" dxfId="32" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18024,7 +20950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759D5263-CE33-4927-93AA-6232274D84F9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18051,29 +20977,29 @@
       <c r="B1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="45"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="45"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -18165,11 +21091,11 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>1.1000000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
-        <v>0.1</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
@@ -18341,15 +21267,25 @@
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
         <v>1 m. 0 mėn. 3 d.</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
+      <c r="D8" s="10">
+        <v>46249</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46249</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.02</v>
+      </c>
       <c r="J8" s="9"/>
       <c r="X8" s="6">
         <f t="shared" si="1"/>
@@ -18367,7 +21303,9 @@
       <c r="B9" s="6">
         <v>46065</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="10">
+        <v>46280</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="17" t="str">
         <f t="shared" si="0"/>
@@ -18379,11 +21317,11 @@
       <c r="J9" s="14"/>
       <c r="X9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46249</v>
       </c>
       <c r="Y9" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -18393,7 +21331,9 @@
       <c r="B10" s="6">
         <v>46066</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="10">
+        <v>46310</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="17" t="str">
         <f t="shared" si="0"/>
@@ -18419,7 +21359,9 @@
       <c r="B11" s="6">
         <v>46433</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="10">
+        <v>46341</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="17" t="str">
         <f t="shared" si="0"/>
@@ -18444,9 +21386,11 @@
       </c>
       <c r="B12" s="17">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>195</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>168</v>
+      </c>
+      <c r="D12" s="10">
+        <v>46371</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="17" t="str">
         <f t="shared" si="0"/>
@@ -18468,7 +21412,9 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
+      <c r="D13" s="10">
+        <v>46402</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="17" t="str">
         <f t="shared" si="0"/>
@@ -18491,7 +21437,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <v>46433</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="17" t="str">
         <f t="shared" si="0"/>
@@ -19308,11 +22256,11 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1.1000000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.12000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -19323,1342 +22271,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="2">
+    <cfRule type="expression" dxfId="30" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="31" priority="7">
+    <cfRule type="expression" dxfId="29" priority="7">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="30" priority="8">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B61398-82DC-4A18-83BA-B3E07706D6C6}">
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="10">
-        <v>46096</v>
-      </c>
-      <c r="E3" s="10">
-        <v>46096</v>
-      </c>
-      <c r="F3" s="17">
-        <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>1</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0.11000000000000001</v>
-      </c>
-      <c r="N3" s="7" t="str">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2" t="str">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="13"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46042</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-21.2</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="10">
-        <v>46127</v>
-      </c>
-      <c r="E4" s="10">
-        <v>46127</v>
-      </c>
-      <c r="F4" s="17">
-        <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46096</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="10">
-        <v>46157</v>
-      </c>
-      <c r="E5" s="10">
-        <v>46157</v>
-      </c>
-      <c r="F5" s="17">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.17</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>46127</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="10">
-        <v>46188</v>
-      </c>
-      <c r="E6" s="10">
-        <v>46188</v>
-      </c>
-      <c r="F6" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.18</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>46157</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="10">
-        <v>46218</v>
-      </c>
-      <c r="E7" s="10">
-        <v>46218</v>
-      </c>
-      <c r="F7" s="17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.17</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>46188</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>1 m. 0 mėn. 26 d.</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="9"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>46218</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46042</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="14"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46045</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46433</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="14"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="17">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>195</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="14"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
-      <c r="N13" s="13"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="24"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="14"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="3">
-        <v>21.2</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="14"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="14"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="14"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="10"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="14"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="10"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="14"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="10"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="14"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="14"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="10"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="10"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="10"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="10"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="10"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="10"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="10"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="14"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="10"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="14"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="10"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="14"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="10"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="10"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="10"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="14"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="10"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="14"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="10"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="14"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="10"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="10"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="14"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="10"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="14"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="10"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="14"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="10"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="17" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>1</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0.11000000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="29" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="27" priority="7">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="26" priority="8">
+    <cfRule type="expression" dxfId="28" priority="8">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
